--- a/target/classes/common-templates/templates/age-rating-template.xlsx
+++ b/target/classes/common-templates/templates/age-rating-template.xlsx
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -123,6 +123,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -488,7 +491,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.005" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -506,13 +509,11 @@
       <c r="C1" s="4" t="n"/>
       <c r="D1" s="4" t="n"/>
       <c r="E1" s="4" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
       <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
-      <c r="K1" s="4" t="n"/>
-      <c r="L1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="6" t="n"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="3" t="n"/>
@@ -520,22 +521,27 @@
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="3" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="6" t="n"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
       <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
       <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+      <c r="N3" s="6" t="n"/>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="6" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="1" t="n"/>
@@ -566,10 +572,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="J1:R1"/>
+    <mergeCell ref="J2:R2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
